--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-12-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_09-12-2025.xlsx
@@ -581,23 +581,23 @@
   (Session info: chrome=143.0.7499.40); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7b5828255
-	0x7ff7b58282b0
-	0x7ff7b560165d
-	0x7ff7b5659a33
-	0x7ff7b5659d3c
-	0x7ff7b56adf67
-	0x7ff7b56aac97
-	0x7ff7b564ac29
-	0x7ff7b564ba93
-	0x7ff7b5b3fff0
-	0x7ff7b5b3a930
-	0x7ff7b5b59096
-	0x7ff7b5845754
-	0x7ff7b584e6fc
-	0x7ff7b5831974
-	0x7ff7b5831b25
-	0x7ff7b5817852
+	0x7ff6dd278255
+	0x7ff6dd2782b0
+	0x7ff6dd05165d
+	0x7ff6dd0a9a33
+	0x7ff6dd0a9d3c
+	0x7ff6dd0fdf67
+	0x7ff6dd0fac97
+	0x7ff6dd09ac29
+	0x7ff6dd09ba93
+	0x7ff6dd58fff0
+	0x7ff6dd58a930
+	0x7ff6dd5a9096
+	0x7ff6dd295754
+	0x7ff6dd29e6fc
+	0x7ff6dd281974
+	0x7ff6dd281b25
+	0x7ff6dd267852
 	0x7fff459ae8d7
 	0x7fff46e2c53c
 </t>
